--- a/SNH48成员名单生日表2603.xlsx
+++ b/SNH48成员名单生日表2603.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -519,7 +519,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -556,6 +556,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0"/>
@@ -897,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1042"/>
+  <dimension ref="A1:H1053"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9" customWidth="1" style="3" min="1" max="1"/>
@@ -29245,7 +29246,7 @@
       </c>
       <c r="H1041" s="3" t="n"/>
     </row>
-    <row r="1042">
+    <row r="1042" s="12">
       <c r="A1042" s="3" t="n">
         <v>84</v>
       </c>
@@ -29272,6 +29273,314 @@
         <v>23</v>
       </c>
       <c r="H1042" s="3" t="n"/>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B1043" s="2" t="inlineStr">
+        <is>
+          <t>GNZ48二十一期生</t>
+        </is>
+      </c>
+      <c r="C1043" s="3" t="inlineStr">
+        <is>
+          <t>陈柯睿</t>
+        </is>
+      </c>
+      <c r="D1043" s="6" t="n">
+        <v>40394</v>
+      </c>
+      <c r="E1043" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F1043" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G1043" s="0" t="n">
+        <v>44</v>
+      </c>
+      <c r="H1043" s="3" t="n"/>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B1044" s="2" t="inlineStr">
+        <is>
+          <t>GNZ48二十一期生</t>
+        </is>
+      </c>
+      <c r="C1044" s="3" t="inlineStr">
+        <is>
+          <t>何颖莹</t>
+        </is>
+      </c>
+      <c r="D1044" s="6" t="n">
+        <v>39683</v>
+      </c>
+      <c r="E1044" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F1044" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1044" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1044" s="3" t="n"/>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B1045" s="2" t="inlineStr">
+        <is>
+          <t>GNZ48二十一期生</t>
+        </is>
+      </c>
+      <c r="C1045" s="3" t="inlineStr">
+        <is>
+          <t>贺宇晨</t>
+        </is>
+      </c>
+      <c r="D1045" s="6" t="n">
+        <v>38723</v>
+      </c>
+      <c r="E1045" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F1045" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="G1045" s="0" t="n">
+        <v>254</v>
+      </c>
+      <c r="H1045" s="3" t="n"/>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B1046" s="2" t="inlineStr">
+        <is>
+          <t>GNZ48二十一期生</t>
+        </is>
+      </c>
+      <c r="C1046" s="3" t="inlineStr">
+        <is>
+          <t>贾佳慧</t>
+        </is>
+      </c>
+      <c r="D1046" s="6" t="n">
+        <v>38237</v>
+      </c>
+      <c r="E1046" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F1046" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1046" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1046" s="3" t="n"/>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B1047" s="2" t="inlineStr">
+        <is>
+          <t>GNZ48二十一期生</t>
+        </is>
+      </c>
+      <c r="C1047" s="3" t="inlineStr">
+        <is>
+          <t>李若竹</t>
+        </is>
+      </c>
+      <c r="D1047" s="6" t="n">
+        <v>39145</v>
+      </c>
+      <c r="E1047" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F1047" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="G1047" s="0" t="n">
+        <v>197</v>
+      </c>
+      <c r="H1047" s="3" t="n"/>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B1048" s="2" t="inlineStr">
+        <is>
+          <t>GNZ48二十一期生</t>
+        </is>
+      </c>
+      <c r="C1048" s="3" t="inlineStr">
+        <is>
+          <t>刘媛媛</t>
+        </is>
+      </c>
+      <c r="D1048" s="6" t="n">
+        <v>38405</v>
+      </c>
+      <c r="E1048" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F1048" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1048" s="0" t="n">
+        <v>207</v>
+      </c>
+      <c r="H1048" s="3" t="n"/>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B1049" s="2" t="inlineStr">
+        <is>
+          <t>GNZ48二十一期生</t>
+        </is>
+      </c>
+      <c r="C1049" s="3" t="inlineStr">
+        <is>
+          <t>罗晶</t>
+        </is>
+      </c>
+      <c r="D1049" s="6" t="n">
+        <v>39228</v>
+      </c>
+      <c r="E1049" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F1049" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="G1049" s="0" t="n">
+        <v>114</v>
+      </c>
+      <c r="H1049" s="3" t="n"/>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B1050" s="2" t="inlineStr">
+        <is>
+          <t>GNZ48二十一期生</t>
+        </is>
+      </c>
+      <c r="C1050" s="3" t="inlineStr">
+        <is>
+          <t>陶佳妮</t>
+        </is>
+      </c>
+      <c r="D1050" s="6" t="n">
+        <v>39887</v>
+      </c>
+      <c r="E1050" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F1050" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="G1050" s="0" t="n">
+        <v>186</v>
+      </c>
+      <c r="H1050" s="3" t="n"/>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B1051" s="2" t="inlineStr">
+        <is>
+          <t>GNZ48二十一期生</t>
+        </is>
+      </c>
+      <c r="C1051" s="3" t="inlineStr">
+        <is>
+          <t>王唯祎</t>
+        </is>
+      </c>
+      <c r="D1051" s="6" t="n">
+        <v>39448</v>
+      </c>
+      <c r="E1051" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F1051" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1051" s="0" t="n">
+        <v>259</v>
+      </c>
+      <c r="H1051" s="3" t="n"/>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B1052" s="2" t="inlineStr">
+        <is>
+          <t>GNZ48二十一期生</t>
+        </is>
+      </c>
+      <c r="C1052" s="3" t="inlineStr">
+        <is>
+          <t>向吴怡轩</t>
+        </is>
+      </c>
+      <c r="D1052" s="6" t="n">
+        <v>39275</v>
+      </c>
+      <c r="E1052" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F1052" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="G1052" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="H1052" s="3" t="n"/>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B1053" s="2" t="inlineStr">
+        <is>
+          <t>GNZ48二十一期生</t>
+        </is>
+      </c>
+      <c r="C1053" s="3" t="inlineStr">
+        <is>
+          <t>周文迪</t>
+        </is>
+      </c>
+      <c r="D1053" s="6" t="n">
+        <v>38620</v>
+      </c>
+      <c r="E1053" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F1053" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="G1053" s="0" t="n">
+        <v>357</v>
+      </c>
+      <c r="H1053" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/SNH48成员名单生日表2603.xlsx
+++ b/SNH48成员名单生日表2603.xlsx
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1053"/>
+  <dimension ref="A1:H1061"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9" customWidth="1" style="3" min="1" max="1"/>
@@ -29554,7 +29554,7 @@
       </c>
       <c r="H1052" s="3" t="n"/>
     </row>
-    <row r="1053">
+    <row r="1053" s="12">
       <c r="A1053" s="3" t="n">
         <v>81</v>
       </c>
@@ -29581,6 +29581,230 @@
         <v>357</v>
       </c>
       <c r="H1053" s="3" t="n"/>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B1054" s="2" t="inlineStr">
+        <is>
+          <t>BEJ48十九期生</t>
+        </is>
+      </c>
+      <c r="C1054" s="3" t="inlineStr">
+        <is>
+          <t>范小天</t>
+        </is>
+      </c>
+      <c r="D1054" s="6" t="n">
+        <v>38369</v>
+      </c>
+      <c r="E1054" s="6" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F1054" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1054" s="0" t="n">
+        <v>252</v>
+      </c>
+      <c r="H1054" s="3" t="n"/>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B1055" s="2" t="inlineStr">
+        <is>
+          <t>BEJ48十九期生</t>
+        </is>
+      </c>
+      <c r="C1055" s="3" t="inlineStr">
+        <is>
+          <t>刘雨硕</t>
+        </is>
+      </c>
+      <c r="D1055" s="6" t="n">
+        <v>38566</v>
+      </c>
+      <c r="E1055" s="6" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F1055" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1055" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="H1055" s="3" t="n"/>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B1056" s="2" t="inlineStr">
+        <is>
+          <t>BEJ48十九期生</t>
+        </is>
+      </c>
+      <c r="C1056" s="3" t="inlineStr">
+        <is>
+          <t>刘卓尔</t>
+        </is>
+      </c>
+      <c r="D1056" s="6" t="n">
+        <v>38128</v>
+      </c>
+      <c r="E1056" s="6" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F1056" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1056" s="0" t="n">
+        <v>128</v>
+      </c>
+      <c r="H1056" s="3" t="n"/>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B1057" s="2" t="inlineStr">
+        <is>
+          <t>BEJ48十九期生</t>
+        </is>
+      </c>
+      <c r="C1057" s="3" t="inlineStr">
+        <is>
+          <t>李祉瑶</t>
+        </is>
+      </c>
+      <c r="D1057" s="6" t="n">
+        <v>39957</v>
+      </c>
+      <c r="E1057" s="6" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F1057" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="G1057" s="0" t="n">
+        <v>125</v>
+      </c>
+      <c r="H1057" s="3" t="n"/>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B1058" s="2" t="inlineStr">
+        <is>
+          <t>BEJ48十九期生</t>
+        </is>
+      </c>
+      <c r="C1058" s="3" t="inlineStr">
+        <is>
+          <t>武佳凝</t>
+        </is>
+      </c>
+      <c r="D1058" s="6" t="n">
+        <v>40046</v>
+      </c>
+      <c r="E1058" s="6" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F1058" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="G1058" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="H1058" s="3" t="n"/>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B1059" s="2" t="inlineStr">
+        <is>
+          <t>BEJ48十九期生</t>
+        </is>
+      </c>
+      <c r="C1059" s="3" t="inlineStr">
+        <is>
+          <t>王馨怡</t>
+        </is>
+      </c>
+      <c r="D1059" s="6" t="n">
+        <v>39839</v>
+      </c>
+      <c r="E1059" s="6" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F1059" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="G1059" s="0" t="n">
+        <v>243</v>
+      </c>
+      <c r="H1059" s="3" t="n"/>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B1060" s="2" t="inlineStr">
+        <is>
+          <t>BEJ48十九期生</t>
+        </is>
+      </c>
+      <c r="C1060" s="3" t="inlineStr">
+        <is>
+          <t>张旭</t>
+        </is>
+      </c>
+      <c r="D1060" s="6" t="n">
+        <v>39200</v>
+      </c>
+      <c r="E1060" s="6" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F1060" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="G1060" s="0" t="n">
+        <v>151</v>
+      </c>
+      <c r="H1060" s="3" t="n"/>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B1061" s="2" t="inlineStr">
+        <is>
+          <t>BEJ48十九期生</t>
+        </is>
+      </c>
+      <c r="C1061" s="3" t="inlineStr">
+        <is>
+          <t>张怡璐</t>
+        </is>
+      </c>
+      <c r="D1061" s="6" t="n">
+        <v>38293</v>
+      </c>
+      <c r="E1061" s="6" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F1061" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1061" s="0" t="n">
+        <v>328</v>
+      </c>
+      <c r="H1061" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
